--- a/E/DND05S.xlsx
+++ b/E/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
   <si>
     <t/>
   </si>
@@ -1105,25 +1105,25 @@
     <t>10012548</t>
   </si>
   <si>
-    <t>SOKLIN RLX/LAV RF770</t>
+    <t>SOKLIN RLX/LAV RF760</t>
   </si>
   <si>
     <t>10003646</t>
   </si>
   <si>
-    <t>SO KLIN P/L APPLE770</t>
+    <t>SO KLIN P/L APPLE760</t>
   </si>
   <si>
     <t>10003645</t>
   </si>
   <si>
-    <t>SO KLIN P/L LMN 780</t>
+    <t>SO KLIN P/L LMN 760</t>
   </si>
   <si>
     <t>20101095</t>
   </si>
   <si>
-    <t>SO KLN LNT SEREH 770</t>
+    <t>SO KLN LNT SEREH 760</t>
   </si>
   <si>
     <t>20131223</t>
@@ -1255,9 +1255,6 @@
     <t>LFBY CC PRG LME2X610</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20134576</t>
   </si>
   <si>
@@ -1967,27 +1964,6 @@
   </si>
   <si>
     <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
   </si>
 </sst>
 </file>
@@ -2380,14 +2356,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6128,15 +6103,15 @@
         <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>414</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -6153,10 +6128,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -6173,10 +6148,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -6193,10 +6168,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -6213,16 +6188,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>4</v>
@@ -6233,16 +6208,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
@@ -6253,16 +6228,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -6273,16 +6248,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>14</v>
@@ -6293,16 +6268,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>18</v>
@@ -6313,16 +6288,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>4</v>
@@ -6333,16 +6308,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>8</v>
@@ -6353,16 +6328,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>11</v>
@@ -6373,16 +6348,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
@@ -6393,16 +6368,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>18</v>
@@ -6413,16 +6388,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>32</v>
@@ -6433,16 +6408,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>35</v>
@@ -6453,16 +6428,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>70</v>
@@ -6473,16 +6448,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>135</v>
@@ -6493,16 +6468,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>4</v>
@@ -6513,16 +6488,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>8</v>
@@ -6533,16 +6508,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>11</v>
@@ -6553,16 +6528,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6573,16 +6548,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>18</v>
@@ -6593,16 +6568,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>32</v>
@@ -6613,16 +6588,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>35</v>
@@ -6633,36 +6608,36 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>70</v>
@@ -6673,36 +6648,36 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>4</v>
@@ -6713,16 +6688,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>8</v>
@@ -6733,16 +6708,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>11</v>
@@ -6753,16 +6728,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>14</v>
@@ -6773,16 +6748,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6793,16 +6768,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>32</v>
@@ -6813,16 +6788,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>35</v>
@@ -6833,16 +6808,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>38</v>
@@ -6853,16 +6828,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>70</v>
@@ -6873,16 +6848,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>135</v>
@@ -6893,16 +6868,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>144</v>
@@ -6913,16 +6888,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>155</v>
@@ -6933,16 +6908,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>169</v>
@@ -6953,16 +6928,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>169</v>
@@ -6973,16 +6948,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>169</v>
@@ -6993,16 +6968,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>169</v>
@@ -7013,16 +6988,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
@@ -7033,16 +7008,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>4</v>
@@ -7053,16 +7028,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>8</v>
@@ -7073,16 +7048,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7093,16 +7068,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>14</v>
@@ -7113,16 +7088,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>18</v>
@@ -7133,16 +7108,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>32</v>
@@ -7153,16 +7128,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>35</v>
@@ -7173,16 +7148,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>38</v>
@@ -7193,16 +7168,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>70</v>
@@ -7213,16 +7188,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>135</v>
@@ -7233,16 +7208,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>144</v>
@@ -7253,16 +7228,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>155</v>
@@ -7273,16 +7248,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="C245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>4</v>
@@ -7293,16 +7268,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>8</v>
@@ -7313,16 +7288,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>11</v>
@@ -7333,16 +7308,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>14</v>
@@ -7353,16 +7328,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>18</v>
@@ -7373,16 +7348,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -7393,16 +7368,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>35</v>
@@ -7413,16 +7388,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>38</v>
@@ -7433,16 +7408,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>70</v>
@@ -7453,16 +7428,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>135</v>
@@ -7473,16 +7448,16 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>144</v>
@@ -7493,16 +7468,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>155</v>
@@ -7513,16 +7488,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>169</v>
@@ -7533,16 +7508,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>188</v>
@@ -7553,16 +7528,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>208</v>
@@ -7573,16 +7548,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>217</v>
@@ -7593,16 +7568,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>226</v>
@@ -7613,16 +7588,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>4</v>
@@ -7633,16 +7608,16 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>8</v>
@@ -7653,16 +7628,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>11</v>
@@ -7673,16 +7648,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>14</v>
@@ -7693,16 +7668,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>18</v>
@@ -7713,16 +7688,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>32</v>
@@ -7733,16 +7708,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>35</v>
@@ -7753,16 +7728,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>38</v>
@@ -7773,16 +7748,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>70</v>
@@ -7793,16 +7768,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>135</v>
@@ -7813,16 +7788,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>144</v>
@@ -7833,16 +7808,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>155</v>
@@ -7853,16 +7828,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>169</v>
@@ -7873,16 +7848,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>4</v>
@@ -7893,16 +7868,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>8</v>
@@ -7913,16 +7888,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>11</v>
@@ -7933,36 +7908,36 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>18</v>
@@ -7973,16 +7948,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>32</v>
@@ -7993,16 +7968,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>35</v>
@@ -8013,16 +7988,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>38</v>
@@ -8033,16 +8008,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>70</v>
@@ -8053,16 +8028,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>135</v>
@@ -8073,16 +8048,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>144</v>
@@ -8093,16 +8068,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>155</v>
@@ -8113,16 +8088,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>169</v>
@@ -8133,16 +8108,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>4</v>
@@ -8153,16 +8128,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>8</v>
@@ -8173,16 +8148,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>11</v>
@@ -8193,16 +8168,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>14</v>
@@ -8213,16 +8188,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>18</v>
@@ -8233,16 +8208,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>32</v>
@@ -8253,16 +8228,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>35</v>
@@ -8273,16 +8248,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>38</v>
@@ -8293,16 +8268,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>70</v>
@@ -8313,16 +8288,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>135</v>
@@ -8333,16 +8308,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>144</v>
@@ -8353,16 +8328,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>155</v>
@@ -8373,82 +8348,22 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F303" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DND05S.xlsx
+++ b/E/DND05S.xlsx
@@ -1180,7 +1180,7 @@
     <t>20131788</t>
   </si>
   <si>
-    <t>MAMA LMN JR.NPS 950</t>
+    <t>MAMA LMN JR.NPS 920</t>
   </si>
   <si>
     <t>27</t>
@@ -1189,7 +1189,7 @@
     <t>20142275</t>
   </si>
   <si>
-    <t>MAMA LIME CHARCO 950</t>
+    <t>MAMA LIME CHARCO 920</t>
   </si>
   <si>
     <t>20034450</t>

--- a/E/DND05S.xlsx
+++ b/E/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="654">
   <si>
     <t/>
   </si>
@@ -100,13 +100,13 @@
     <t>20067585</t>
   </si>
   <si>
-    <t>SKLN LQD SC/BLOSM675</t>
+    <t>SKLN LQD SC/BLOSM700</t>
   </si>
   <si>
     <t>20054747</t>
   </si>
   <si>
-    <t>SKLIN LQD V/BLSOM675</t>
+    <t>SKLIN LQD V/BLSOM700</t>
   </si>
   <si>
     <t>6</t>
@@ -115,7 +115,7 @@
     <t>20046548</t>
   </si>
   <si>
-    <t>SKLIN LQD SFTRGN 675</t>
+    <t>SKLIN LQD SFTRGN 700</t>
   </si>
   <si>
     <t>7</t>
@@ -202,25 +202,25 @@
     <t>20093627</t>
   </si>
   <si>
-    <t>SKLN LQD SKR STRW500</t>
+    <t>SKLN LQD SKR STRW510</t>
   </si>
   <si>
     <t>20123818</t>
   </si>
   <si>
-    <t>SKLN LQD PROV LVD500</t>
+    <t>SKLN LQD PROV LVD510</t>
   </si>
   <si>
     <t>20091870</t>
   </si>
   <si>
-    <t>SKLN LQ WHT&amp;BRGHT500</t>
+    <t>SKLN LQ WHT&amp;BRGHT510</t>
   </si>
   <si>
     <t>20114428</t>
   </si>
   <si>
-    <t>SKLN LQD KOR CMLA500</t>
+    <t>SKLN LQD KOR CMLA510</t>
   </si>
   <si>
     <t>9</t>
@@ -259,6 +259,12 @@
     <t>LARIST SMR.BRZ 700ML</t>
   </si>
   <si>
+    <t>20143785</t>
+  </si>
+  <si>
+    <t>IDM D/C AUTUM SNT700</t>
+  </si>
+  <si>
     <t>20139955</t>
   </si>
   <si>
@@ -976,6 +982,12 @@
     <t>IDM PURPOSE CLN 400</t>
   </si>
   <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
     <t>10014263</t>
   </si>
   <si>
@@ -1312,21 +1324,15 @@
     <t>SNLGHT BIO NATURE600</t>
   </si>
   <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
     <t>20139947</t>
   </si>
   <si>
@@ -1369,6 +1375,12 @@
     <t>STELA A/F RJ AMPT350</t>
   </si>
   <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
     <t>10004032</t>
   </si>
   <si>
@@ -1405,7 +1417,7 @@
     <t>10005246</t>
   </si>
   <si>
-    <t>WING PRCLN CLN BR750</t>
+    <t>WING PRCLN CLN BR700</t>
   </si>
   <si>
     <t>20040315</t>
@@ -1684,286 +1696,283 @@
     <t>SOFEL LOT.KRN/SMR 60</t>
   </si>
   <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
     <t>20078241</t>
   </si>
   <si>
     <t>SOFFELL LOT.APEL 60G</t>
   </si>
   <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -2356,13 +2365,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3063,7 +3073,7 @@
         <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3077,10 +3087,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -3100,7 +3110,7 @@
         <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3120,7 +3130,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -3140,7 +3150,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -3160,18 +3170,18 @@
         <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3180,10 +3190,10 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,7 +3210,7 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3220,7 +3230,7 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3237,10 +3247,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3260,7 +3270,7 @@
         <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -3280,10 +3290,10 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,10 +3310,10 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,7 +3330,7 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3340,7 +3350,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3360,7 +3370,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3380,7 +3390,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3397,10 +3407,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3420,7 +3430,7 @@
         <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3450,10 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3460,10 +3470,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3477,13 +3487,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,7 +3510,7 @@
         <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3520,7 +3530,7 @@
         <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3540,7 +3550,7 @@
         <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3557,10 +3567,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3568,22 +3578,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3597,13 +3607,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3617,10 +3627,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3637,10 +3647,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3648,19 +3658,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3677,10 +3687,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3697,10 +3707,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3717,10 +3727,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3737,10 +3747,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3748,22 +3758,22 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3777,33 +3787,33 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3817,13 +3827,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,13 +3847,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,30 +3867,30 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3897,10 +3907,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3917,10 +3927,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3937,10 +3947,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3957,10 +3967,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3977,10 +3987,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3997,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4017,13 +4027,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4037,33 +4047,33 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4077,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>15</v>
@@ -4097,10 +4107,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4117,10 +4127,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>15</v>
@@ -4137,13 +4147,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,13 +4167,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,13 +4187,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4217,30 +4227,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -4257,10 +4267,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4277,10 +4287,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -4297,33 +4307,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,13 +4347,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,13 +4367,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4377,30 +4387,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -4417,10 +4427,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -4437,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4457,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4477,33 +4487,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4517,10 +4527,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -4537,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,10 +4567,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4577,33 +4587,33 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="E112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4637,10 +4647,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4657,10 +4667,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4677,13 +4687,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4697,13 +4707,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4717,13 +4727,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4737,13 +4747,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4757,13 +4767,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,30 +4787,30 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4817,10 +4827,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4837,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4857,10 +4867,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4877,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4897,10 +4907,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4917,10 +4927,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4937,30 +4947,30 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>21</v>
@@ -4977,13 +4987,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4997,33 +5007,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>294</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5037,13 +5047,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,10 +5067,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -5077,10 +5087,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -5097,13 +5107,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5117,30 +5127,30 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -5157,33 +5167,33 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,13 +5207,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5217,13 +5227,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5237,13 +5247,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5257,50 +5267,50 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5317,10 +5327,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5337,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5357,13 +5367,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5377,13 +5387,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5397,53 +5407,53 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>339</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>294</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="E154" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5457,13 +5467,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5477,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5497,13 +5507,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5517,13 +5527,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5537,13 +5547,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5557,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5577,53 +5587,53 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5637,13 +5647,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,13 +5667,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,10 +5687,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5697,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5717,10 +5727,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5737,10 +5747,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5748,39 +5758,39 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5797,13 +5807,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5817,10 +5827,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5837,10 +5847,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5857,13 +5867,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,10 +5887,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5888,39 +5898,39 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5937,10 +5947,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5957,10 +5967,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5977,10 +5987,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5997,10 +6007,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6017,13 +6027,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6037,50 +6047,50 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>249</v>
+        <v>77</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>21</v>
@@ -6097,13 +6107,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6117,10 +6127,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>21</v>
@@ -6137,13 +6147,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6157,13 +6167,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6177,13 +6187,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6197,50 +6207,50 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6257,13 +6267,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6277,10 +6287,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6297,30 +6307,30 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6328,19 +6338,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6357,10 +6367,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6377,13 +6387,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,13 +6407,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,13 +6427,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,13 +6447,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,13 +6467,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,50 +6487,50 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6537,13 +6547,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,13 +6567,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,13 +6587,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6597,13 +6607,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>160</v>
+        <v>296</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,53 +6627,53 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>469</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>312</v>
+        <v>162</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6677,53 +6687,53 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>294</v>
+        <v>473</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6737,13 +6747,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6767,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6777,13 +6787,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6797,13 +6807,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6817,13 +6827,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6837,10 +6847,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>77</v>
@@ -6857,13 +6867,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6877,13 +6887,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6897,10 +6907,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -6917,13 +6927,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6937,13 +6947,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6957,13 +6967,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6977,13 +6987,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6997,13 +7007,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,53 +7027,53 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>339</v>
+        <v>77</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,13 +7087,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7097,13 +7107,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,13 +7127,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,13 +7147,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,13 +7167,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,13 +7187,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7197,13 +7207,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,13 +7227,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7237,13 +7247,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7257,53 +7267,53 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="C247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7317,13 +7327,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7337,13 +7347,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7357,13 +7367,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7377,13 +7387,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7397,13 +7407,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>294</v>
+        <v>343</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,13 +7427,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7437,13 +7447,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,13 +7467,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,13 +7487,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,13 +7507,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,13 +7527,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,13 +7547,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,13 +7567,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7577,13 +7587,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,33 +7607,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7637,13 +7647,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,13 +7667,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,13 +7687,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7697,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7717,13 +7727,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,13 +7747,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,10 +7767,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>5</v>
@@ -7777,13 +7787,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7797,13 +7807,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7817,10 +7827,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>77</v>
@@ -7837,10 +7847,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>77</v>
@@ -7863,7 +7873,7 @@
         <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7883,7 +7893,7 @@
         <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7903,7 +7913,7 @@
         <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7923,15 +7933,15 @@
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>605</v>
+        <v>314</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
@@ -7943,7 +7953,7 @@
         <v>18</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>312</v>
+        <v>607</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7963,7 +7973,7 @@
         <v>32</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7983,7 +7993,7 @@
         <v>35</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8023,7 +8033,7 @@
         <v>70</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8040,10 +8050,10 @@
         <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8060,7 +8070,7 @@
         <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>5</v>
@@ -8080,7 +8090,7 @@
         <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>5</v>
@@ -8100,10 +8110,10 @@
         <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8123,7 +8133,7 @@
         <v>4</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8143,7 +8153,7 @@
         <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8163,7 +8173,7 @@
         <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8183,7 +8193,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8203,7 +8213,7 @@
         <v>18</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8223,7 +8233,7 @@
         <v>32</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,7 +8253,7 @@
         <v>35</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,7 +8310,7 @@
         <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8320,7 +8330,7 @@
         <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8340,10 +8350,10 @@
         <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,10 +8370,30 @@
         <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/E/DND05S.xlsx
+++ b/E/DND05S.xlsx
@@ -667,7 +667,7 @@
     <t>20064413</t>
   </si>
   <si>
-    <t>ATCK JAZ1 S/CNTA 1.4</t>
+    <t>ATCK JAZ1 S/CNTA 1.3</t>
   </si>
   <si>
     <t>16</t>
@@ -676,19 +676,19 @@
     <t>20064414</t>
   </si>
   <si>
-    <t>ATTACK JAZ1 P/SGR1.4</t>
+    <t>ATTACK JAZ1 P/SGR1.3</t>
   </si>
   <si>
     <t>20130527</t>
   </si>
   <si>
-    <t>ATTACK DET+SF RB 1.4</t>
+    <t>ATTACK DET+SF RB 1.2</t>
   </si>
   <si>
     <t>20138108</t>
   </si>
   <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
+    <t>JAZ 1 PRPL BLS 1.2KG</t>
   </si>
   <si>
     <t>20071827</t>
@@ -715,7 +715,7 @@
     <t>20074992</t>
   </si>
   <si>
-    <t>BUKRIM OXY/K VIOL700</t>
+    <t>BUKRIM OXY/K VIOL650</t>
   </si>
   <si>
     <t>20119238</t>
@@ -7830,7 +7830,7 @@
         <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>77</v>
@@ -7850,7 +7850,7 @@
         <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>77</v>
